--- a/TFM_mao/resultados/technical_batch/anova_moa_fine.xlsx
+++ b/TFM_mao/resultados/technical_batch/anova_moa_fine.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,6 +446,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>P_adj</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Veredicto</t>
         </is>
       </c>
@@ -462,7 +467,10 @@
       <c r="C2" t="n">
         <v>2.009384512214811e-05</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>2.511730640268513e-05</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -480,7 +488,10 @@
       <c r="C3" t="n">
         <v>8.079275472416612e-30</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="n">
+        <v>4.847565283449967e-29</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -498,7 +509,10 @@
       <c r="C4" t="n">
         <v>0.01510291836322621</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" t="n">
+        <v>0.0161816982463138</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -516,7 +530,10 @@
       <c r="C5" t="n">
         <v>3.491073141831787e-19</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" t="n">
+        <v>9.521108568632148e-19</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -534,7 +551,10 @@
       <c r="C6" t="n">
         <v>6.581736909471477e-17</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" t="n">
+        <v>1.410372194886745e-16</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -552,7 +572,10 @@
       <c r="C7" t="n">
         <v>2.139961855032596e-71</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" t="n">
+        <v>3.209942782548894e-70</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -570,7 +593,10 @@
       <c r="C8" t="n">
         <v>5.035776507097571e-25</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" t="n">
+        <v>2.158189931613245e-24</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -588,7 +614,10 @@
       <c r="C9" t="n">
         <v>9.957604537685591e-43</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" t="n">
+        <v>7.468203403264193e-42</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -606,7 +635,10 @@
       <c r="C10" t="n">
         <v>7.186131008707711e-09</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" t="n">
+        <v>1.026590144101102e-08</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -624,7 +656,10 @@
       <c r="C11" t="n">
         <v>1.366549614930615e-60</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" t="n">
+        <v>1.366549614930615e-59</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -642,7 +677,10 @@
       <c r="C12" t="n">
         <v>4.184089387041874e-24</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" t="n">
+        <v>1.569033520140703e-23</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -660,7 +698,10 @@
       <c r="C13" t="n">
         <v>5.569830325262933e-18</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" t="n">
+        <v>1.392457581315733e-17</v>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -678,7 +719,10 @@
       <c r="C14" t="n">
         <v>2.265303728738748e-11</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" t="n">
+        <v>3.576795361166444e-11</v>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -696,7 +740,10 @@
       <c r="C15" t="n">
         <v>1.40895341512687e-124</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" t="n">
+        <v>4.22686024538061e-123</v>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -714,7 +761,10 @@
       <c r="C16" t="n">
         <v>9.617953380898487e-10</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" t="n">
+        <v>1.442693007134773e-09</v>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -732,7 +782,10 @@
       <c r="C17" t="n">
         <v>2.751277340230319e-05</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" t="n">
+        <v>3.301532808276383e-05</v>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -750,7 +803,10 @@
       <c r="C18" t="n">
         <v>1.996536280897473e-15</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" t="n">
+        <v>3.743505526682762e-15</v>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -768,7 +824,10 @@
       <c r="C19" t="n">
         <v>8.22601606475747e-16</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" t="n">
+        <v>1.645203212951494e-15</v>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -786,7 +845,10 @@
       <c r="C20" t="n">
         <v>2.840777167664631e-13</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" t="n">
+        <v>5.013136178231702e-13</v>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -804,7 +866,10 @@
       <c r="C21" t="n">
         <v>8.003950633152266e-13</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" t="n">
+        <v>1.333991772192044e-12</v>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -822,7 +887,10 @@
       <c r="C22" t="n">
         <v>9.386789682158829e-23</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" t="n">
+        <v>3.128929894052943e-22</v>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -840,7 +908,10 @@
       <c r="C23" t="n">
         <v>1.324375982491161e-17</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" t="n">
+        <v>3.056252267287295e-17</v>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -858,7 +929,10 @@
       <c r="C24" t="n">
         <v>3.147681669391488e-05</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" t="n">
+        <v>3.63194038775941e-05</v>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -876,7 +950,10 @@
       <c r="C25" t="n">
         <v>5.590165325464791e-07</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" t="n">
+        <v>7.622952716542897e-07</v>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -894,7 +971,10 @@
       <c r="C26" t="n">
         <v>1.143557747182326e-25</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" t="n">
+        <v>5.717788735911629e-25</v>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -912,7 +992,10 @@
       <c r="C27" t="n">
         <v>0.425270742417127</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" t="n">
+        <v>0.425270742417127</v>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>No significativo</t>
         </is>
@@ -930,7 +1013,10 @@
       <c r="C28" t="n">
         <v>1.392088562544789e-05</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" t="n">
+        <v>1.815767690275812e-05</v>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -948,7 +1034,10 @@
       <c r="C29" t="n">
         <v>4.250349151583261e-05</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" t="n">
+        <v>4.722610168425845e-05</v>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -966,7 +1055,10 @@
       <c r="C30" t="n">
         <v>9.111367650110441e-22</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" t="n">
+        <v>2.733410295033132e-21</v>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -984,7 +1076,10 @@
       <c r="C31" t="n">
         <v>0.2193412314376346</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" t="n">
+        <v>0.2269047221768634</v>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>No significativo</t>
         </is>
